--- a/5_cobranza/inputs/correcciones_lote.xlsx
+++ b/5_cobranza/inputs/correcciones_lote.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +29,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00065F46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -59,34 +55,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00FFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00FFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00FFFFFF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00FFFFFF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -503,42 +490,6 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Corregido desde discrepancias_cobranza.xlsx</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>13/06/2026 11:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/5_cobranza/inputs/correcciones_lote.xlsx
+++ b/5_cobranza/inputs/correcciones_lote.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -71,9 +75,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -441,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -490,6 +503,252 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026 07:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026 07:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026 07:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Corregido a mano: C1-9 es el lote real (Roberto Macarlopu, COFOPRI); la regla auto-recuperada tenia el sentido al reves.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026 08:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026 07:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Huerfano en discrepancias_cobranza: cobrador Wagner escribio G-36, el lote real es C-36 (MARIA NORABUENA ESPADA).</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026 08:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Identidad a proposito: bloquea que el auto-sanador (lee trazabilidad vieja, ciclo 17) reinserte C1-9-&gt;C1-17. C1-9 es el lote real.</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026 09:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/5_cobranza/inputs/correcciones_lote.xlsx
+++ b/5_cobranza/inputs/correcciones_lote.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +29,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00065F46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -75,18 +71,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -503,252 +490,6 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>10/08/2026 07:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>10/08/2026 07:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>10/08/2026 07:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Corregido a mano: C1-9 es el lote real (Roberto Macarlopu, COFOPRI); la regla auto-recuperada tenia el sentido al reves.</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>10/08/2026 08:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Recuperado desde trazabilidad_cobranza.xlsx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>10/08/2026 07:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Huerfano en discrepancias_cobranza: cobrador Wagner escribio G-36, el lote real es C-36 (MARIA NORABUENA ESPADA).</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>10/08/2026 08:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Identidad a proposito: bloquea que el auto-sanador (lee trazabilidad vieja, ciclo 17) reinserte C1-9-&gt;C1-17. C1-9 es el lote real.</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>10/08/2026 09:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
